--- a/exports/ICICILIFE_full_report.xlsx
+++ b/exports/ICICILIFE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.63</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>609.45</v>
+        <v>575</v>
       </c>
       <c r="I2" t="n">
         <v>582.5470885861607</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.56</v>
+        <v>-2.29</v>
       </c>
       <c r="L2" t="n">
-        <v>2.31</v>
+        <v>3.99</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05</v>
+        <v>1.39</v>
       </c>
       <c r="N2" t="n">
-        <v>1.33</v>
+        <v>6.11</v>
       </c>
       <c r="O2" t="n">
         <v>0.95</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44636.55208333334</v>
+        <v>44637.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>469</v>
+        <v>485.75</v>
       </c>
       <c r="I3" t="n">
         <v>479.9068806387812</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K3" t="n">
-        <v>18.43</v>
+        <v>15.52</v>
       </c>
       <c r="L3" t="n">
         <v>4.52</v>
@@ -612,7 +647,7 @@
         <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>3.48</v>
+        <v>5.27</v>
       </c>
       <c r="O3" t="n">
         <v>-6.11</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.92</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="I4" t="n">
         <v>515.5566770709249</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>8.699999999999999</v>
+        <v>5.61</v>
       </c>
       <c r="L4" t="n">
         <v>3.94</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.4</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44707.38541666666</v>
+        <v>44707.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>521.1</v>
+        <v>529</v>
       </c>
       <c r="I5" t="n">
         <v>528.5598517842792</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36.83333333333334</v>
+        <v>37</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.58</v>
+        <v>-3.12</v>
       </c>
       <c r="L5" t="n">
         <v>5.16</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.34</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44726.55208333334</v>
+        <v>44727.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>532.85</v>
+        <v>527.8</v>
       </c>
       <c r="I6" t="n">
         <v>528.4721997038098</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>0.73</v>
+        <v>-0.23</v>
       </c>
       <c r="L6" t="n">
         <v>2.54</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44748.55208333334</v>
+        <v>44749.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>509.45</v>
+        <v>519.75</v>
       </c>
       <c r="I7" t="n">
         <v>514.4701032060459</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>3.48</v>
+        <v>1.53</v>
       </c>
       <c r="L7" t="n">
         <v>1.89</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.38</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44784.38541666666</v>
+        <v>44784.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>552.7</v>
+        <v>546.25</v>
       </c>
       <c r="I8" t="n">
         <v>547.078765239079</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K8" t="n">
-        <v>6.34</v>
+        <v>5.1</v>
       </c>
       <c r="L8" t="n">
         <v>3.34</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>6.61</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44790.55208333334</v>
+        <v>44791.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>581.95</v>
+        <v>592.9</v>
       </c>
       <c r="I9" t="n">
         <v>582.3309535475787</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.54</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>7.2</v>
+        <v>10.55</v>
       </c>
       <c r="M9" t="n">
         <v>0.2</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>6.53</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="I10" t="n">
         <v>565.2560863144838</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.19</v>
+        <v>-4.71</v>
       </c>
       <c r="L10" t="n">
-        <v>4.46</v>
+        <v>4.71</v>
       </c>
       <c r="M10" t="n">
         <v>1.64</v>
       </c>
       <c r="N10" t="n">
-        <v>2.64</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.92</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>5.73</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44896.55208333334</v>
+        <v>44897.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>476.5</v>
+        <v>478.6</v>
       </c>
       <c r="I11" t="n">
         <v>477.8197693007629</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>76.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="K11" t="n">
-        <v>15.66</v>
+        <v>15.29</v>
       </c>
       <c r="L11" t="n">
         <v>1.95</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>4.84</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>461.85</v>
+        <v>457.85</v>
       </c>
       <c r="I12" t="n">
         <v>459.3687145982569</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.5</v>
+        <v>-4.34</v>
       </c>
       <c r="L12" t="n">
-        <v>3.83</v>
+        <v>4.51</v>
       </c>
       <c r="M12" t="n">
         <v>-0</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>5.09</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44928.55208333334</v>
+        <v>44929.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>453.5</v>
+        <v>466</v>
       </c>
       <c r="I13" t="n">
         <v>460.3727100484944</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>0.95</v>
+        <v>-1.78</v>
       </c>
       <c r="L13" t="n">
-        <v>1.71</v>
+        <v>2.22</v>
       </c>
       <c r="M13" t="n">
         <v>0.83</v>
       </c>
       <c r="N13" t="n">
-        <v>1.63</v>
+        <v>3.64</v>
       </c>
       <c r="O13" t="n">
         <v>-1.27</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.14</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44950.55208333334</v>
+        <v>44951.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>469.85</v>
+        <v>463.7</v>
       </c>
       <c r="I14" t="n">
         <v>463.9212479647355</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K14" t="n">
-        <v>0.83</v>
+        <v>-0.49</v>
       </c>
       <c r="L14" t="n">
         <v>3.22</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>4.91</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45000.55208333334</v>
+        <v>45001.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>384.5</v>
+        <v>413.8</v>
       </c>
       <c r="I15" t="n">
         <v>405.6195413765354</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K15" t="n">
-        <v>17.08</v>
+        <v>10.76</v>
       </c>
       <c r="L15" t="n">
         <v>1.66</v>
@@ -1296,7 +1475,7 @@
         <v>0.73</v>
       </c>
       <c r="N15" t="n">
-        <v>2.88</v>
+        <v>6.61</v>
       </c>
       <c r="O15" t="n">
         <v>-1.46</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.5</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45041.55208333334</v>
+        <v>45042.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>434.75</v>
+        <v>428.4</v>
       </c>
       <c r="I16" t="n">
         <v>430.8433113866814</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K16" t="n">
-        <v>5.06</v>
+        <v>3.53</v>
       </c>
       <c r="L16" t="n">
         <v>8</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>7.24</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45055.55208333334</v>
+        <v>45056.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>445</v>
+        <v>450.55</v>
       </c>
       <c r="I17" t="n">
         <v>448.4831597831205</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.87</v>
+        <v>-5.17</v>
       </c>
       <c r="L17" t="n">
-        <v>5.02</v>
+        <v>5.86</v>
       </c>
       <c r="M17" t="n">
         <v>0.97</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>4.92</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45062.55208333334</v>
+        <v>45063.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>433.6</v>
+        <v>421.3</v>
       </c>
       <c r="I18" t="n">
         <v>431.2105876808333</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.76</v>
+        <v>-6.49</v>
       </c>
       <c r="L18" t="n">
-        <v>4.67</v>
+        <v>6.78</v>
       </c>
       <c r="M18" t="n">
         <v>0.35</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.36</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45072.38541666666</v>
+        <v>45072.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>442.55</v>
+        <v>446.2</v>
       </c>
       <c r="I19" t="n">
         <v>443.9596300138214</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.04</v>
+        <v>-5.91</v>
       </c>
       <c r="L19" t="n">
-        <v>5.6</v>
+        <v>6.15</v>
       </c>
       <c r="M19" t="n">
         <v>0.99</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.43</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45124.55208333334</v>
+        <v>45125.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>583.2</v>
+        <v>570.95</v>
       </c>
       <c r="I20" t="n">
         <v>576.7571654121467</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>52</v>
+        <v>52.83333333333334</v>
       </c>
       <c r="K20" t="n">
-        <v>30.7</v>
+        <v>27.96</v>
       </c>
       <c r="L20" t="n">
         <v>0.92</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.65</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45167.55208333334</v>
+        <v>45168.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>557.5</v>
+        <v>562.7</v>
       </c>
       <c r="I21" t="n">
         <v>559.8788765622364</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K21" t="n">
-        <v>2.36</v>
+        <v>1.44</v>
       </c>
       <c r="L21" t="n">
         <v>3.14</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>5.68</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45174.38541666666</v>
+        <v>45174.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>540.7</v>
+        <v>536.55</v>
       </c>
       <c r="I22" t="n">
         <v>536.6913481949722</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.91</v>
+        <v>-4.65</v>
       </c>
       <c r="L22" t="n">
-        <v>4.03</v>
+        <v>4.9</v>
       </c>
       <c r="M22" t="n">
         <v>0.07000000000000001</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>5.83</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45176.55208333334</v>
+        <v>45177.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>547</v>
+        <v>565.2</v>
       </c>
       <c r="I23" t="n">
         <v>564.3487067015242</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.95</v>
+        <v>-5.34</v>
       </c>
       <c r="L23" t="n">
-        <v>2.36</v>
+        <v>5.83</v>
       </c>
       <c r="M23" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="N23" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="O23" t="n">
         <v>-3.03</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>7.79</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45198.38541666666</v>
+        <v>45198.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>568</v>
+        <v>564.05</v>
       </c>
       <c r="I24" t="n">
         <v>565.7796900357416</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="L24" t="n">
         <v>3.44</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.48</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45237.38541666666</v>
+        <v>45237.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>520.05</v>
+        <v>539</v>
       </c>
       <c r="I25" t="n">
         <v>534.5617426562936</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>38.83333333333334</v>
+        <v>39</v>
       </c>
       <c r="K25" t="n">
-        <v>7.8</v>
+        <v>4.44</v>
       </c>
       <c r="L25" t="n">
         <v>1.04</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.17</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45271.38541666666</v>
+        <v>45271.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>540.35</v>
+        <v>538.25</v>
       </c>
       <c r="I26" t="n">
         <v>538.5335533417584</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>33.83333333333334</v>
+        <v>34</v>
       </c>
       <c r="K26" t="n">
-        <v>0.25</v>
+        <v>-0.14</v>
       </c>
       <c r="L26" t="n">
         <v>3.52</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.29</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45293.55208333334</v>
+        <v>45294.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>534.15</v>
+        <v>538.5</v>
       </c>
       <c r="I27" t="n">
         <v>536.2859606609604</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>0.76</v>
+        <v>-0.05</v>
       </c>
       <c r="L27" t="n">
         <v>3.09</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>3.73</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45306.38541666666</v>
+        <v>45306.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>526.55</v>
+        <v>521.6</v>
       </c>
       <c r="I28" t="n">
         <v>525.20741755113</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.22</v>
+        <v>-3.14</v>
       </c>
       <c r="L28" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="M28" t="n">
         <v>0.09</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>4.72</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45322.55208333334</v>
+        <v>45323.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>502.9</v>
+        <v>513.5</v>
       </c>
       <c r="I29" t="n">
         <v>509.0907569285583</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>3.59</v>
+        <v>1.55</v>
       </c>
       <c r="L29" t="n">
         <v>1.05</v>
@@ -2094,7 +2441,7 @@
         <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="O29" t="n">
         <v>-1.57</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.11</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45369.55208333334</v>
+        <v>45370.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>565.5</v>
+        <v>554.3</v>
       </c>
       <c r="I30" t="n">
         <v>558.5032214969021</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K30" t="n">
-        <v>10.13</v>
+        <v>7.95</v>
       </c>
       <c r="L30" t="n">
         <v>3.15</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>8.15</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45373.55208333334</v>
+        <v>45377.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>578.2</v>
+        <v>599</v>
       </c>
       <c r="I31" t="n">
         <v>589.8486880537154</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.31</v>
+        <v>-8.06</v>
       </c>
       <c r="L31" t="n">
-        <v>6.22</v>
+        <v>9.32</v>
       </c>
       <c r="M31" t="n">
-        <v>0.18</v>
+        <v>1.69</v>
       </c>
       <c r="N31" t="n">
-        <v>3.15</v>
+        <v>3.31</v>
       </c>
       <c r="O31" t="n">
         <v>-2.92</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>7.43</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45400.55208333334</v>
+        <v>45401.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>609</v>
+        <v>587.25</v>
       </c>
       <c r="I32" t="n">
         <v>598.122456637985</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K32" t="n">
-        <v>1.67</v>
+        <v>-1.96</v>
       </c>
       <c r="L32" t="n">
-        <v>1.84</v>
+        <v>3.41</v>
       </c>
       <c r="M32" t="n">
-        <v>1.12</v>
+        <v>3.28</v>
       </c>
       <c r="N32" t="n">
-        <v>2.17</v>
+        <v>3.78</v>
       </c>
       <c r="O32" t="n">
         <v>3.31</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.68</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>571.95</v>
+        <v>581.55</v>
       </c>
       <c r="I33" t="n">
         <v>577.8272105600391</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K33" t="n">
-        <v>2.61</v>
+        <v>0.97</v>
       </c>
       <c r="L33" t="n">
         <v>2.96</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.35</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>755.15</v>
+        <v>742.7</v>
       </c>
       <c r="I34" t="n">
         <v>753.2143630514271</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>116.1666666666667</v>
+        <v>119</v>
       </c>
       <c r="K34" t="n">
-        <v>29.85</v>
+        <v>27.71</v>
       </c>
       <c r="L34" t="n">
         <v>2.48</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>162</v>
+        <v>163</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.99</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45660.38541666666</v>
+        <v>45660.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>670.8</v>
+        <v>676.2</v>
       </c>
       <c r="I35" t="n">
         <v>674.5893098258631</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>88</v>
+        <v>88.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>9.68</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L35" t="n">
         <v>4.6</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.28</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45670.38541666666</v>
+        <v>45670.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>640.8</v>
+        <v>636.25</v>
       </c>
       <c r="I36" t="n">
         <v>640.4738591490942</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.24</v>
+        <v>-5.91</v>
       </c>
       <c r="L36" t="n">
         <v>6.48</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.73</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45735.55208333334</v>
+        <v>45736.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>564.6</v>
+        <v>577.9</v>
       </c>
       <c r="I37" t="n">
         <v>565.3999665929671</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>65</v>
+        <v>65.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>11.26</v>
+        <v>9.17</v>
       </c>
       <c r="L37" t="n">
         <v>4.83</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>5.76</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45744.38541666666</v>
+        <v>45744.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>583.7</v>
+        <v>565.45</v>
       </c>
       <c r="I38" t="n">
         <v>571.0888121170639</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>-2.15</v>
       </c>
       <c r="L38" t="n">
-        <v>2.23</v>
+        <v>2.95</v>
       </c>
       <c r="M38" t="n">
         <v>0.68</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>7.66</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>572.5</v>
+        <v>585.75</v>
       </c>
       <c r="I39" t="n">
         <v>572.6107554863764</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.25</v>
+        <v>-3.59</v>
       </c>
       <c r="L39" t="n">
-        <v>3.23</v>
+        <v>6.51</v>
       </c>
       <c r="M39" t="n">
-        <v>0.59</v>
+        <v>1.48</v>
       </c>
       <c r="N39" t="n">
         <v>3.91</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>6.59</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>588.9</v>
+        <v>579</v>
       </c>
       <c r="I40" t="n">
         <v>579.3420856457999</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>0.54</v>
+        <v>-1.15</v>
       </c>
       <c r="L40" t="n">
         <v>1.64</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>6.38</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45791.55208333334</v>
+        <v>45792.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>607</v>
+        <v>611.35</v>
       </c>
       <c r="I41" t="n">
         <v>609.4538106231138</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.84</v>
+        <v>-5.59</v>
       </c>
       <c r="L41" t="n">
-        <v>5.43</v>
+        <v>5.66</v>
       </c>
       <c r="M41" t="n">
         <v>2.13</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.12</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45813.38541666666</v>
+        <v>45813.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>641.15</v>
+        <v>638.15</v>
       </c>
       <c r="I42" t="n">
         <v>640.9775985901319</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>4.87</v>
+        <v>4.38</v>
       </c>
       <c r="L42" t="n">
         <v>2.27</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>4.25</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45835.55208333334</v>
+        <v>45838.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>647.7</v>
+        <v>654.8</v>
       </c>
       <c r="I43" t="n">
         <v>650.7688236444087</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>22</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.5</v>
+        <v>-2.61</v>
       </c>
       <c r="L43" t="n">
-        <v>1.97</v>
+        <v>3.24</v>
       </c>
       <c r="M43" t="n">
         <v>0.63</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>4.78</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45854.55208333334</v>
+        <v>45855.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>651</v>
+        <v>642.25</v>
       </c>
       <c r="I44" t="n">
         <v>648.5954030667901</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.58</v>
+        <v>-1.92</v>
       </c>
       <c r="L44" t="n">
         <v>2.73</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.28</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45882.55208333334</v>
+        <v>45883.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>620</v>
+        <v>629.4</v>
       </c>
       <c r="I45" t="n">
         <v>625.0073462583388</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K45" t="n">
-        <v>3.46</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
         <v>1.82</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>4.88</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45897.38541666666</v>
+        <v>45897.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>615.15</v>
+        <v>609.95</v>
       </c>
       <c r="I46" t="n">
         <v>612.0859071267836</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.26</v>
+        <v>-3.09</v>
       </c>
       <c r="L46" t="n">
-        <v>2.57</v>
+        <v>3.51</v>
       </c>
       <c r="M46" t="n">
         <v>0.32</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>4.38</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45951.57291666666</v>
+        <v>45953.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>595.55</v>
+        <v>609.8</v>
       </c>
       <c r="I47" t="n">
         <v>605.1995934735411</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>54.02083333333334</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="K47" t="n">
-        <v>2.36</v>
+        <v>0.02</v>
       </c>
       <c r="L47" t="n">
         <v>4.93</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.55</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45985.38541666666</v>
+        <v>45985.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>611.3</v>
+        <v>604.85</v>
       </c>
       <c r="I48" t="n">
         <v>609.615176093668</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K48" t="n">
-        <v>0.25</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L48" t="n">
         <v>3.39</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>4.66</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46000.55208333334</v>
+        <v>46001.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>623.25</v>
+        <v>644.4</v>
       </c>
       <c r="I49" t="n">
         <v>630.0991002713569</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.04</v>
+        <v>-6.54</v>
       </c>
       <c r="L49" t="n">
-        <v>4.95</v>
+        <v>6.78</v>
       </c>
       <c r="M49" t="n">
         <v>0.49</v>
       </c>
       <c r="N49" t="n">
-        <v>1.66</v>
+        <v>3.23</v>
       </c>
       <c r="O49" t="n">
         <v>-0.84</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.54</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46036.38541666666</v>
+        <v>46036.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>673.75</v>
+        <v>667</v>
       </c>
       <c r="I50" t="n">
         <v>667.7518656261058</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K50" t="n">
-        <v>4.55</v>
+        <v>3.51</v>
       </c>
       <c r="L50" t="n">
         <v>3.94</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.33</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46056.55208333334</v>
+        <v>46057.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>656.5</v>
+        <v>661.9</v>
       </c>
       <c r="I51" t="n">
         <v>660.2937147670074</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>1.57</v>
+        <v>0.76</v>
       </c>
       <c r="L51" t="n">
         <v>2.51</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>6.75</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>654.3</v>
+        <v>627.25</v>
       </c>
       <c r="I52" t="n">
         <v>646.1535021216276</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.15</v>
+        <v>-5.23</v>
       </c>
       <c r="L52" t="n">
-        <v>4.84</v>
+        <v>5.73</v>
       </c>
       <c r="M52" t="n">
         <v>1.81</v>
       </c>
       <c r="N52" t="n">
-        <v>2.3</v>
+        <v>4.48</v>
       </c>
       <c r="O52" t="n">
         <v>0.4</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.45</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>517</v>
+        <v>541.95</v>
       </c>
       <c r="I53" t="n">
         <v>539.7402939631452</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K53" t="n">
-        <v>17.58</v>
+        <v>13.6</v>
       </c>
       <c r="L53" t="n">
         <v>3.63</v>
       </c>
       <c r="M53" t="n">
-        <v>2.26</v>
+        <v>4.64</v>
       </c>
       <c r="N53" t="n">
-        <v>1.72</v>
+        <v>4.67</v>
       </c>
       <c r="O53" t="n">
         <v>-4.48</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>7.76</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>533.95</v>
+        <v>518.7</v>
       </c>
       <c r="I54" t="n">
         <v>530.1885568919118</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.48</v>
+        <v>-4.29</v>
       </c>
       <c r="L54" t="n">
-        <v>2.21</v>
+        <v>4.45</v>
       </c>
       <c r="M54" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N54" t="n">
-        <v>2.36</v>
+        <v>3.87</v>
       </c>
       <c r="O54" t="n">
         <v>4.67</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>7.97</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46147.55208333334</v>
+        <v>46148.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>535.5</v>
+        <v>546.3</v>
       </c>
       <c r="I55" t="n">
         <v>544.992190755736</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.24</v>
+        <v>-5.32</v>
       </c>
       <c r="L55" t="n">
-        <v>4.24</v>
+        <v>6.02</v>
       </c>
       <c r="M55" t="n">
         <v>1.04</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>6.13</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46157.38541666666</v>
+        <v>46157.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>537.5</v>
+        <v>534.4</v>
       </c>
       <c r="I56" t="n">
         <v>536.8723255912807</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.61</v>
+        <v>-2.18</v>
       </c>
       <c r="L56" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="M56" t="n">
         <v>0.79</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>5.5</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>468.5</v>
+        <v>488.55</v>
       </c>
       <c r="I57" t="n">
         <v>484.5449825735491</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>28</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>12.33</v>
+        <v>8.58</v>
       </c>
       <c r="L57" t="n">
         <v>0.78</v>
       </c>
       <c r="M57" t="n">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="N57" t="n">
-        <v>2.45</v>
+        <v>3.31</v>
       </c>
       <c r="O57" t="n">
         <v>-1.57</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.83</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46198.38541666666</v>
+        <v>46198.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>495</v>
+        <v>491.1</v>
       </c>
       <c r="I58" t="n">
         <v>491.9540269496832</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>1.32</v>
+        <v>0.52</v>
       </c>
       <c r="L58" t="n">
         <v>2.64</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>5.38</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46212.55208333334</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>492.05</v>
+        <v>508.85</v>
       </c>
       <c r="I59" t="n">
         <v>506.7984155307111</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.19</v>
+        <v>-3.61</v>
       </c>
       <c r="L59" t="n">
-        <v>1.9</v>
+        <v>4.17</v>
       </c>
       <c r="M59" t="n">
         <v>0.89</v>
       </c>
       <c r="N59" t="n">
-        <v>2.41</v>
+        <v>3.79</v>
       </c>
       <c r="O59" t="n">
         <v>-1.19</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.79</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46241.55208333334</v>
+        <v>46244.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>502.1</v>
+        <v>497.15</v>
       </c>
       <c r="I60" t="n">
         <v>500.827315042075</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.33</v>
+        <v>-2.3</v>
       </c>
       <c r="L60" t="n">
         <v>3.65</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>4.66</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46259.55208333334</v>
+        <v>46260.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>508</v>
+        <v>524.65</v>
       </c>
       <c r="I61" t="n">
         <v>517.1040888646812</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.18</v>
+        <v>-5.53</v>
       </c>
       <c r="L61" t="n">
-        <v>4.78</v>
+        <v>5.75</v>
       </c>
       <c r="M61" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="N61" t="n">
         <v>2.35</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.72</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46266.38541666666</v>
+        <v>46266.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>501.55</v>
+        <v>495.5</v>
       </c>
       <c r="I62" t="n">
         <v>498.451170495491</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.4</v>
+        <v>-5.56</v>
       </c>
       <c r="L62" t="n">
-        <v>5.42</v>
+        <v>5.65</v>
       </c>
       <c r="M62" t="n">
         <v>0.34</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>5.21</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46281.55208333334</v>
+        <v>46282.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>474</v>
+        <v>494.45</v>
       </c>
       <c r="I63" t="n">
         <v>484.0707241398853</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>4.34</v>
+        <v>0.21</v>
       </c>
       <c r="L63" t="n">
         <v>1.82</v>
@@ -4032,7 +4787,7 @@
         <v>0.66</v>
       </c>
       <c r="N63" t="n">
-        <v>3.21</v>
+        <v>3.67</v>
       </c>
       <c r="O63" t="n">
         <v>-1.29</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.73</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46289.38541666666</v>
+        <v>46289.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>470.65</v>
+        <v>464.8</v>
       </c>
       <c r="I64" t="n">
         <v>467.6620896887326</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.81</v>
+        <v>-6</v>
       </c>
       <c r="L64" t="n">
         <v>9.93</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>43</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6251,7 +7038,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.4</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="6">
@@ -6261,7 +7048,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -6271,7 +7058,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>116.2</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8">
@@ -6281,7 +7068,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -6291,7 +7078,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.6</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="10">
@@ -6301,7 +7088,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.4</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="11">
@@ -6311,7 +7098,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -6321,7 +7108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6331,7 +7118,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.3</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6341,7 +7128,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.65</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="15">
@@ -6351,7 +7138,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.23</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="16">
@@ -6361,7 +7148,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.09</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="17">
@@ -6371,7 +7158,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.7</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="18">
@@ -6381,7 +7168,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.1</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="19">
@@ -6391,7 +7178,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.51</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="20">
@@ -6401,7 +7188,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.23</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="21">
@@ -6411,7 +7198,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.93</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="22">
@@ -6421,7 +7208,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -6431,7 +7218,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6441,7 +7228,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="25">
@@ -6461,7 +7248,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.81</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="27">
@@ -6471,7 +7258,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.87</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="28">
@@ -6481,7 +7268,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
